--- a/production-lines-issue-tracker/excel/Production-Lines-Issue-Tracker.xlsx
+++ b/production-lines-issue-tracker/excel/Production-Lines-Issue-Tracker.xlsx
@@ -43,58 +43,58 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0012181D"/>
+      <color rgb="FF12181D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000E6E7D"/>
+      <color rgb="FF0E6E7D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="007A8894"/>
+      <color rgb="FF7A8894"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0012181D"/>
+      <color rgb="FF12181D"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0047535E"/>
+      <color rgb="FF47535E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0012181D"/>
+      <color rgb="FF12181D"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0012181D"/>
+      <color rgb="FF12181D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="007A8894"/>
+      <color rgb="FF7A8894"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0012181D"/>
+      <color rgb="FF12181D"/>
       <sz val="22"/>
     </font>
   </fonts>
@@ -107,12 +107,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E6E7D"/>
+        <fgColor rgb="FF0E6E7D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FA"/>
+        <fgColor rgb="FFF7F9FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,16 +126,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D5DCE2"/>
+        <color rgb="FFD5DCE2"/>
       </left>
       <right style="thin">
-        <color rgb="00D5DCE2"/>
+        <color rgb="FFD5DCE2"/>
       </right>
       <top style="thin">
-        <color rgb="00D5DCE2"/>
+        <color rgb="FFD5DCE2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D5DCE2"/>
+        <color rgb="FFD5DCE2"/>
       </bottom>
     </border>
   </borders>
@@ -190,66 +190,56 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00C23B2E"/>
-        <sz val="10"/>
+        <color rgb="FFC23B2E"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FAE7E4"/>
+          <fgColor rgb="FFFAE7E4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00B57312"/>
-        <sz val="10"/>
+        <color rgb="FFB57312"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F7EEDC"/>
+          <fgColor rgb="FFF7EEDC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
         <b val="1"/>
-        <color rgb="003D6E9E"/>
-        <sz val="10"/>
+        <color rgb="FF3D6E9E"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E6EEF6"/>
+          <fgColor rgb="FFE6EEF6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
         <b val="1"/>
-        <color rgb="007A8894"/>
-        <sz val="10"/>
+        <color rgb="FF7A8894"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EDF0F2"/>
+          <fgColor rgb="FFEDF0F2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
         <b val="1"/>
-        <color rgb="002E7D5B"/>
-        <sz val="10"/>
+        <color rgb="FF2E7D5B"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E2F0E9"/>
+          <fgColor rgb="FFE2F0E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6703,22 +6693,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
       <formula1>=TicketTypes</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
       <formula1>=LineCodes</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
       <formula1>=Categories</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
       <formula1>=Severities</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
+    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
       <formula1>=Statuses</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
+    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Use the dropdown so the Dashboard counts stay right. Add new options on the Choices sheet." type="list">
       <formula1>=Shifts</formula1>
     </dataValidation>
   </dataValidations>
